--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_292_R30.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_292_R30.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0158</v>
+        <v>5.266</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3772</v>
+        <v>5.5265</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3614</v>
+        <v>-0.2606</v>
       </c>
       <c r="G2" t="n">
         <v>5.3946</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1419</v>
+        <v>0.3921</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1968</v>
+        <v>0.3462</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0549</v>
+        <v>0.0459</v>
       </c>
       <c r="V2" t="n">
         <v>-2.1444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.092</v>
+        <v>4.4504</v>
       </c>
       <c r="E3" t="n">
-        <v>2.965</v>
+        <v>3.189</v>
       </c>
       <c r="F3" t="n">
-        <v>1.127</v>
+        <v>1.2614</v>
       </c>
       <c r="G3" t="n">
         <v>2.3787</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3216</v>
+        <v>0.68</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2205</v>
+        <v>0.4446</v>
       </c>
       <c r="U3" t="n">
-        <v>0.101</v>
+        <v>0.2355</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6683</v>
+        <v>3.2354</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3404</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0087</v>
+        <v>3.9415</v>
       </c>
       <c r="G4" t="n">
         <v>4.1435</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8855</v>
+        <v>1.4525</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3293</v>
+        <v>0.9636</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5562</v>
+        <v>0.489</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5051</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5648</v>
+        <v>3.0834</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8453</v>
+        <v>2.3302</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7195</v>
+        <v>0.7531</v>
       </c>
       <c r="G5" t="n">
         <v>2.545</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4141</v>
+        <v>0.9326</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4391</v>
+        <v>0.9241</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.025</v>
+        <v>0.0086</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3943</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6534</v>
+        <v>2.7514</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3133</v>
+        <v>2.674</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3401</v>
+        <v>0.0774</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8833</v>
+        <v>2.8138</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5654</v>
+        <v>1.2245</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3179</v>
+        <v>1.5893</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7861</v>
+        <v>3.9436</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6757</v>
+        <v>1.983</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1104</v>
+        <v>1.9606</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0972</v>
+        <v>-1.1298</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8897</v>
+        <v>-0.7584</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2075</v>
+        <v>-0.3713</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8423</v>
+        <v>-0.0108</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6869</v>
+        <v>0.1221</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1554</v>
+        <v>-0.1329</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.6083</v>
+        <v>-0.2836</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6083</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>A. BACOT JR.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9622</v>
+        <v>1.5116</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0528</v>
+        <v>0.1763</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0906</v>
+        <v>1.3353</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8138</v>
+        <v>1.5937</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2245</v>
+        <v>1.0048</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5893</v>
+        <v>0.5889</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9436</v>
+        <v>0.3571</v>
       </c>
       <c r="K7" t="n">
-        <v>1.983</v>
+        <v>0.5546</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9606</v>
+        <v>-0.1975</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1298</v>
+        <v>1.2366</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7584</v>
+        <v>0.4502</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3713</v>
+        <v>0.7863</v>
       </c>
       <c r="P7" t="n">
         <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8</v>
+        <v>0.2221</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4991</v>
+        <v>0.0512</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3009</v>
+        <v>0.1709</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2836</v>
+        <v>-0.5361</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2836</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BACOT JR.</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2518</v>
+        <v>0.8764</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0163</v>
+        <v>0.2084</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2681</v>
+        <v>0.668</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5937</v>
+        <v>1.8833</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0048</v>
+        <v>1.5654</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5889</v>
+        <v>0.3179</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3571</v>
+        <v>0.7861</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5546</v>
+        <v>0.6757</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1975</v>
+        <v>0.1104</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2366</v>
+        <v>1.0972</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4502</v>
+        <v>0.8897</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7863</v>
+        <v>0.2075</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0378</v>
+        <v>1.0653</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1415</v>
+        <v>0.5821</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1037</v>
+        <v>0.4832</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.201</v>
+        <v>0.4608</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4459</v>
+        <v>-1.2533</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6469</v>
+        <v>1.7141</v>
       </c>
       <c r="G9" t="n">
         <v>1.1665</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0378</v>
+        <v>0.2221</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1415</v>
+        <v>0.0512</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1037</v>
+        <v>0.1709</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. BIRSEN</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.494</v>
+        <v>0.0183</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0347</v>
+        <v>-2.3955</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5407</v>
+        <v>2.4138</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3542</v>
+        <v>-2.6781</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2749</v>
+        <v>-0.5232</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6291</v>
+        <v>-2.1549</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7359</v>
+        <v>-2.9347</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7359</v>
+        <v>-0.0469</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-2.8877</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0901</v>
+        <v>0.2566</v>
       </c>
       <c r="N10" t="n">
-        <v>0.461</v>
+        <v>-0.4762</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6291</v>
+        <v>0.7328</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0668</v>
+        <v>0.3973</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0589</v>
+        <v>0.3712</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.67</v>
+        <v>-0.3587</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1363</v>
+        <v>-2.5898</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4664</v>
+        <v>2.2311</v>
       </c>
       <c r="G11" t="n">
         <v>0.6703</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2834</v>
+        <v>0.5946</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2082</v>
+        <v>0.3383</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4916</v>
+        <v>0.2563</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>M. BIRSEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3943</v>
+        <v>-0.4193</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6065</v>
+        <v>-0.96</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2122</v>
+        <v>0.5407</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6781</v>
+        <v>0.3542</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5232</v>
+        <v>-0.2749</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1549</v>
+        <v>0.6291</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.9347</v>
+        <v>-0.7359</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0469</v>
+        <v>-0.7359</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.8877</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2566</v>
+        <v>1.0901</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4762</v>
+        <v>0.461</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7328</v>
+        <v>0.6291</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.644</v>
+        <v>0.0668</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8136</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1696</v>
+        <v>0.0589</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8346</v>
+        <v>-1.3657</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8558</v>
+        <v>-0.5885</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9788</v>
+        <v>-0.7772</v>
       </c>
       <c r="G13" t="n">
         <v>0.4815</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3883</v>
+        <v>0.0806</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2082</v>
+        <v>0.0591</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1801</v>
+        <v>0.0215</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5361</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.0164</v>
+        <v>19.51</v>
       </c>
       <c r="E14" t="n">
-        <v>4.117699999999999</v>
+        <v>5.611199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>13.8988</v>
+        <v>13.8986</v>
       </c>
       <c r="G14" t="n">
         <v>20.747</v>
@@ -1522,7 +1522,7 @@
         <v>13.4055</v>
       </c>
       <c r="K14" t="n">
-        <v>9.943599999999998</v>
+        <v>9.9436</v>
       </c>
       <c r="L14" t="n">
         <v>3.461999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>13.9172</v>
       </c>
       <c r="S14" t="n">
-        <v>4.972999999999999</v>
+        <v>6.4665</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7937</v>
+        <v>4.2877</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1792</v>
+        <v>2.179</v>
       </c>
       <c r="V14" t="n">
         <v>-6.544</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>J. BEGARIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4683</v>
+        <v>1.5142</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2397</v>
+        <v>1.0495</v>
       </c>
       <c r="F15" t="n">
-        <v>1.708</v>
+        <v>0.4647</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0183</v>
+        <v>1.946</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5799</v>
+        <v>1.8054</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4384</v>
+        <v>0.1406</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3929</v>
+        <v>1.8854</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3193</v>
+        <v>1.8485</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0736</v>
+        <v>0.0368</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6254</v>
+        <v>0.0606</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2606</v>
+        <v>-0.0431</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3648</v>
+        <v>0.1038</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9834</v>
+        <v>-0.0786</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6869</v>
+        <v>-0.2122</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2965</v>
+        <v>0.1336</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1418</v>
+        <v>0.1107</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1418</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BEGARIN</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.121</v>
+        <v>0.7891</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8136</v>
+        <v>-0.9861</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3074</v>
+        <v>1.7751</v>
       </c>
       <c r="G16" t="n">
-        <v>1.946</v>
+        <v>1.3238</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8054</v>
+        <v>0.3434</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1406</v>
+        <v>0.9804</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8854</v>
+        <v>0.5914</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8485</v>
+        <v>0.5546</v>
       </c>
       <c r="L16" t="n">
         <v>0.0368</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0606</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0431</v>
+        <v>-0.2112</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1038</v>
+        <v>0.9436</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4718</v>
+        <v>-0.2153</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0237</v>
+        <v>0.1149</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1107</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1885</v>
+        <v>0.611</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.104</v>
+        <v>-1.5293</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2926</v>
+        <v>2.1402</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3238</v>
+        <v>0.2356</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3434</v>
+        <v>0.3662</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9804</v>
+        <v>-0.1306</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5914</v>
+        <v>-1.0616</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5546</v>
+        <v>-0.1982</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0368</v>
+        <v>-0.8635</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7324000000000001</v>
+        <v>1.2972</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2112</v>
+        <v>0.5644</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9436</v>
+        <v>0.7328</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8158</v>
+        <v>-0.7844</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4481</v>
+        <v>-0.4676</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3677</v>
+        <v>-0.3167</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1671</v>
+        <v>0.0421</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8831</v>
+        <v>-1.6551</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0502</v>
+        <v>1.6972</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2356</v>
+        <v>1.0183</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3662</v>
+        <v>0.5799</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1306</v>
+        <v>0.4384</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0616</v>
+        <v>0.3929</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1982</v>
+        <v>0.3193</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.8635</v>
+        <v>0.0736</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2972</v>
+        <v>0.6254</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5644</v>
+        <v>0.2606</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7328</v>
+        <v>0.3648</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2283</v>
+        <v>0.5573</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8215</v>
+        <v>0.2715</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4068</v>
+        <v>0.2858</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2214</v>
+        <v>-0.4859</v>
       </c>
       <c r="E19" t="n">
-        <v>2.597</v>
+        <v>2.0072</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8184</v>
+        <v>-2.4931</v>
       </c>
       <c r="G19" t="n">
         <v>0.2815</v>
@@ -1936,13 +1936,13 @@
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5487</v>
+        <v>0.2842</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6765</v>
+        <v>0.0868</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1278</v>
+        <v>0.1975</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8197</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>E. OKOBO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8809</v>
+        <v>-2.3628</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5211</v>
+        <v>-1.8616</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3599</v>
+        <v>-0.5012</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.807</v>
+        <v>-4.3783</v>
       </c>
       <c r="H20" t="n">
-        <v>-6.8501</v>
+        <v>-3.659</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9569</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.2574</v>
+        <v>-1.8262</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.2539</v>
+        <v>-2.2176</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0035</v>
+        <v>0.3914</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.5496</v>
+        <v>-2.5521</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.5962</v>
+        <v>-1.4414</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9534</v>
+        <v>-1.1107</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
         <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0136</v>
+        <v>-0.8068</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8566</v>
+        <v>-0.5382</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8703</v>
+        <v>-0.2686</v>
       </c>
       <c r="V20" t="n">
-        <v>3.7527</v>
+        <v>2.8223</v>
       </c>
       <c r="W20" t="n">
-        <v>3.7527</v>
+        <v>2.8223</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3385</v>
+        <v>-2.4414</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9957</v>
+        <v>-2.0493</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3428</v>
+        <v>-0.3921</v>
       </c>
       <c r="G21" t="n">
-        <v>-6.9224</v>
+        <v>-7.807</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.5798</v>
+        <v>-6.8501</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.3426</v>
+        <v>-0.9569</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.952</v>
+        <v>-4.2574</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.6665</v>
+        <v>-4.2539</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.2854</v>
+        <v>-0.0035</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9704</v>
+        <v>-3.5496</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9132</v>
+        <v>-2.5962</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0572</v>
+        <v>-0.9534</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S21" t="n">
-        <v>2.2101</v>
+        <v>0.4531</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4381</v>
+        <v>-0.3848</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.228</v>
+        <v>0.838</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6778999999999999</v>
+        <v>3.7527</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6778999999999999</v>
+        <v>3.7527</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. OKOBO</t>
+          <t>M. STRAZEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2494</v>
+        <v>-3.0814</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0411</v>
+        <v>-2.9855</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2083</v>
+        <v>-0.0958</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.3783</v>
+        <v>-3.6824</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.659</v>
+        <v>-2.3876</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-1.2948</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8262</v>
+        <v>-3.4212</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.2176</v>
+        <v>-1.9221</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3914</v>
+        <v>-1.4991</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5521</v>
+        <v>-0.2612</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4414</v>
+        <v>-0.4655</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1107</v>
+        <v>0.2042</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.0876</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.6933</v>
+        <v>-0.9504</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.7177</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9757</v>
+        <v>-0.3139</v>
       </c>
       <c r="V22" t="n">
-        <v>2.8223</v>
+        <v>-0.5361</v>
       </c>
       <c r="W22" t="n">
-        <v>2.8223</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. STRAZEL</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5634</v>
+        <v>-4.3486</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6933</v>
+        <v>-1.8877</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8701</v>
+        <v>-2.461</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6824</v>
+        <v>-2.7623</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3876</v>
+        <v>0.3193</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2948</v>
+        <v>-3.0816</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.4212</v>
+        <v>1.2268</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9221</v>
+        <v>2.7259</v>
       </c>
       <c r="L23" t="n">
         <v>-1.4991</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2612</v>
+        <v>-3.9891</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4655</v>
+        <v>-2.4066</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2042</v>
+        <v>-1.5825</v>
       </c>
       <c r="P23" t="n">
-        <v>2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.4324</v>
+        <v>-0.7281</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3443</v>
+        <v>-0.4007</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0881</v>
+        <v>-0.3275</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5361</v>
+        <v>-0.3943</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7076</v>
+        <v>-5.1071</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8313</v>
+        <v>-4.0009</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8763</v>
+        <v>-1.1062</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.7623</v>
+        <v>-6.9224</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3193</v>
+        <v>-3.5798</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.0816</v>
+        <v>-3.3426</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2268</v>
+        <v>-3.952</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7259</v>
+        <v>-1.6665</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4991</v>
+        <v>-2.2854</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.9891</v>
+        <v>-2.9704</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.4066</v>
+        <v>-1.9132</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5825</v>
+        <v>-1.0572</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
         <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.0871</v>
+        <v>0.4415</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3443</v>
+        <v>0.4329</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7429</v>
+        <v>0.0086</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3943</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3943</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-18.0163</v>
+        <v>-14.8708</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.8987</v>
+        <v>-13.8988</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.117599999999999</v>
+        <v>-0.9722000000000002</v>
       </c>
       <c r="G25" t="n">
         <v>-20.7472</v>
@@ -2374,7 +2374,7 @@
         <v>-12.8511</v>
       </c>
       <c r="I25" t="n">
-        <v>-7.896099999999999</v>
+        <v>-7.8961</v>
       </c>
       <c r="J25" t="n">
         <v>-7.3417</v>
@@ -2404,19 +2404,19 @@
         <v>15.0769</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.972899999999999</v>
+        <v>-1.8275</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.1791</v>
+        <v>-2.179</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.7939</v>
+        <v>0.3517000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>6.543899999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>9.539100000000001</v>
+        <v>9.539099999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-2.9952</v>
